--- a/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/getWorkoutSession-it-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/it/workout-session-controller/getWorkoutSession-it-form.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="46">
   <si>
     <t>Statement: getWorkoutSession(workoutSessionId: string): Promise&lt;ActionResult&lt;WorkoutSessionWithExercises&gt;&gt; — delegates to workoutSessionService.getWorkoutSession() and returns the matching session with exercises wrapped in ActionResult.</t>
   </si>
@@ -82,10 +82,11 @@
     <t>1</t>
   </si>
   <si>
-    <t>Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession(): date = "2024-06-01", duration = 60, notes = "Rest day".</t>
-  </si>
-  <si>
-    <t>getWorkoutSession(seededSession.id)</t>
+    <t xml:space="preserve">Member seeded via userService.createMember(). Exercise seeded via exerciseService.createExercise(). Session seeded via workoutSessionService.createWorkoutSession(): date = "2024-06-01", duration = 60, notes = "Rest day".
+const inputId: string = seededSession.id</t>
+  </si>
+  <si>
+    <t>getWorkoutSession(inputId)</t>
   </si>
   <si>
     <t>{ success: true, data: { id: seededSession.id, memberId: seededMember.id, duration: 60, notes: "Rest day", exercises: [length 1] } }</t>
@@ -100,10 +101,8 @@
     <t>2</t>
   </si>
   <si>
-    <t>Empty database.</t>
-  </si>
-  <si>
-    <t>getWorkoutSession("00000000-0000-0000-0000-000000000000")</t>
+    <t xml:space="preserve">Empty database.
+const inputId: string = "00000000-0000-0000-0000-000000000000"</t>
   </si>
   <si>
     <t>{ success: false, message: defined non-empty string (NotFoundError message) }</t>
@@ -796,7 +795,7 @@
   <cols>
     <col min="1" max="2" width="14" customWidth="1"/>
     <col min="3" max="3" width="80" customWidth="1"/>
-    <col min="4" max="4" width="61" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="5" width="80" customWidth="1"/>
     <col min="6" max="6" width="27" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
@@ -859,10 +858,10 @@
         <v>28</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>25</v>
@@ -896,17 +895,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -918,40 +917,40 @@
         <v>1</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="F5" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="H5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="I5" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>41</v>
-      </c>
       <c r="J5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="K5" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="L5" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="M5" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
@@ -959,7 +958,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1">
         <v>2</v>
@@ -971,28 +970,28 @@
         <v>0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G6" s="1">
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
